--- a/templates/CLIENT_PROFILE.xlsx
+++ b/templates/CLIENT_PROFILE.xlsx
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>{Report_Number}</t>
+          <t>{PI_Number}</t>
         </is>
       </c>
       <c r="C12" s="34"/>

--- a/templates/CLIENT_PROFILE.xlsx
+++ b/templates/CLIENT_PROFILE.xlsx
@@ -5680,7 +5680,11 @@
         <v>84</v>
       </c>
       <c r="B16" s="81"/>
-      <c r="C16" s="82"/>
+      <c r="C16" s="82" t="inlineStr">
+        <is>
+          <t>{Supervising_Officer}</t>
+        </is>
+      </c>
       <c r="D16" s="82"/>
       <c r="E16" s="82"/>
       <c r="F16" s="82"/>
@@ -5893,7 +5897,11 @@
       <c r="K38" s="75"/>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="H41" s="34"/>
+      <c r="H41" s="34" t="inlineStr">
+        <is>
+          <t>{Supervising_Officer}</t>
+        </is>
+      </c>
       <c r="I41" s="34"/>
       <c r="J41" s="34"/>
       <c r="K41" s="34"/>
@@ -5999,13 +6007,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4CDC4EC0-7389-4C6C-B490-974D94B51799}">
-          <x14:formula1>
-            <xm:f>'Officers Name'!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>C16:F16 H41:K41</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4BB98467-D44F-4467-B5BA-8CC997A48061}">
           <x14:formula1>
             <xm:f>TreePlanting!$A$1:$A$5</xm:f>
